--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/0.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/0.xlsx
@@ -426,13 +426,13 @@
         <v>-7.683508405273275</v>
       </c>
       <c r="E2">
-        <v>-4.078114815841134</v>
+        <v>-6.237051213575954</v>
       </c>
       <c r="F2">
-        <v>-6.579051450087714</v>
+        <v>-6.300179078833051</v>
       </c>
       <c r="G2">
-        <v>-10.24599393070893</v>
+        <v>-12.35369909592348</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.426857144671684</v>
       </c>
       <c r="E3">
-        <v>-4.616210739802565</v>
+        <v>-6.869076745404484</v>
       </c>
       <c r="F3">
-        <v>-6.386822995696268</v>
+        <v>-6.242763277410212</v>
       </c>
       <c r="G3">
-        <v>-9.941556162917552</v>
+        <v>-11.85526998062189</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.412211179325235</v>
       </c>
       <c r="E4">
-        <v>-6.896392500618751</v>
+        <v>-6.401855968137102</v>
       </c>
       <c r="F4">
-        <v>-6.713628018346521</v>
+        <v>-5.982805847431074</v>
       </c>
       <c r="G4">
-        <v>-10.27803007989246</v>
+        <v>-12.04155437811668</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.46527096249048</v>
       </c>
       <c r="E5">
-        <v>-6.381776714387091</v>
+        <v>-7.885963697722893</v>
       </c>
       <c r="F5">
-        <v>-6.253016394938363</v>
+        <v>-5.776698097205723</v>
       </c>
       <c r="G5">
-        <v>-9.561495603372601</v>
+        <v>-11.57998487684933</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.53471948608698</v>
       </c>
       <c r="E6">
-        <v>-7.796118773410713</v>
+        <v>-9.086330831410082</v>
       </c>
       <c r="F6">
-        <v>-6.815145686110704</v>
+        <v>-5.861996745406794</v>
       </c>
       <c r="G6">
-        <v>-9.953732349410991</v>
+        <v>-11.86709524928817</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.50932426799594</v>
       </c>
       <c r="E7">
-        <v>-7.404672951713679</v>
+        <v>-9.7316927191912</v>
       </c>
       <c r="F7">
-        <v>-6.357283414112438</v>
+        <v>-5.824694532891329</v>
       </c>
       <c r="G7">
-        <v>-8.842494770425988</v>
+        <v>-11.34261545113805</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.30083499023734</v>
       </c>
       <c r="E8">
-        <v>-8.612607165467686</v>
+        <v>-10.05038860595501</v>
       </c>
       <c r="F8">
-        <v>-6.3781031862307</v>
+        <v>-5.880599392171463</v>
       </c>
       <c r="G8">
-        <v>-10.07981447627413</v>
+        <v>-11.33108813157031</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.81042421531232</v>
       </c>
       <c r="E9">
-        <v>-8.634149116322174</v>
+        <v>-10.7197015927627</v>
       </c>
       <c r="F9">
-        <v>-5.849572062732205</v>
+        <v>-5.430215206901969</v>
       </c>
       <c r="G9">
-        <v>-9.390678074637286</v>
+        <v>-11.9721521014314</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.97246510396375</v>
       </c>
       <c r="E10">
-        <v>-10.37358126740843</v>
+        <v>-11.01304255355756</v>
       </c>
       <c r="F10">
-        <v>-5.565305362950512</v>
+        <v>-5.597647311458013</v>
       </c>
       <c r="G10">
-        <v>-9.209630960185624</v>
+        <v>-11.36297199565903</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.73477099171581</v>
       </c>
       <c r="E11">
-        <v>-11.59638698980363</v>
+        <v>-12.27550865131193</v>
       </c>
       <c r="F11">
-        <v>-5.876235552693514</v>
+        <v>-5.183548931900749</v>
       </c>
       <c r="G11">
-        <v>-9.209816350735823</v>
+        <v>-11.1345509745404</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.0799056344385</v>
       </c>
       <c r="E12">
-        <v>-10.45500323006635</v>
+        <v>-12.4192514732634</v>
       </c>
       <c r="F12">
-        <v>-5.714053640736413</v>
+        <v>-5.133681214252218</v>
       </c>
       <c r="G12">
-        <v>-8.231609733700894</v>
+        <v>-10.5203189762751</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.01972705453142</v>
       </c>
       <c r="E13">
-        <v>-12.20798910385757</v>
+        <v>-12.88118752136383</v>
       </c>
       <c r="F13">
-        <v>-5.741056761332872</v>
+        <v>-4.912824382420022</v>
       </c>
       <c r="G13">
-        <v>-8.283952769222312</v>
+        <v>-10.44423932923711</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.60365816716612</v>
       </c>
       <c r="E14">
-        <v>-12.58728050131801</v>
+        <v>-14.082723001345</v>
       </c>
       <c r="F14">
-        <v>-5.425619424551237</v>
+        <v>-4.542636930517757</v>
       </c>
       <c r="G14">
-        <v>-7.754378041487256</v>
+        <v>-9.911165354867043</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.907108181098712</v>
       </c>
       <c r="E15">
-        <v>-12.76552123825992</v>
+        <v>-13.55015634414694</v>
       </c>
       <c r="F15">
-        <v>-5.175112838270638</v>
+        <v>-4.757662884201647</v>
       </c>
       <c r="G15">
-        <v>-8.364713527652832</v>
+        <v>-9.67192878147161</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.025910347909646</v>
       </c>
       <c r="E16">
-        <v>-13.88415394458266</v>
+        <v>-14.94798758693859</v>
       </c>
       <c r="F16">
-        <v>-4.71783580784245</v>
+        <v>-4.661718058139797</v>
       </c>
       <c r="G16">
-        <v>-7.164564627119623</v>
+        <v>-9.58748007531034</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.062845418805821</v>
       </c>
       <c r="E17">
-        <v>-13.63737928200868</v>
+        <v>-15.8574817781651</v>
       </c>
       <c r="F17">
-        <v>-4.740840398985594</v>
+        <v>-4.225809593234224</v>
       </c>
       <c r="G17">
-        <v>-6.70262103420634</v>
+        <v>-8.726562776186251</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.127736107961712</v>
       </c>
       <c r="E18">
-        <v>-15.00308553018992</v>
+        <v>-16.57133230683823</v>
       </c>
       <c r="F18">
-        <v>-4.276615851150127</v>
+        <v>-3.857427982270062</v>
       </c>
       <c r="G18">
-        <v>-6.835251420146161</v>
+        <v>-8.54664455776348</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.324298249752686</v>
       </c>
       <c r="E19">
-        <v>-15.78083735558528</v>
+        <v>-17.24321293840826</v>
       </c>
       <c r="F19">
-        <v>-4.123673549203851</v>
+        <v>-3.341441240535861</v>
       </c>
       <c r="G19">
-        <v>-5.775175011925056</v>
+        <v>-8.458752884241369</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.2552438678261337</v>
       </c>
       <c r="E20">
-        <v>-17.24890070176189</v>
+        <v>-17.73111072799466</v>
       </c>
       <c r="F20">
-        <v>-3.685810965595075</v>
+        <v>-3.619647604398672</v>
       </c>
       <c r="G20">
-        <v>-6.190665029831286</v>
+        <v>-8.840644175469537</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.542146771792229</v>
       </c>
       <c r="E21">
-        <v>-16.87726242537441</v>
+        <v>-19.58834660191646</v>
       </c>
       <c r="F21">
-        <v>-3.827102280020975</v>
+        <v>-3.016085860840508</v>
       </c>
       <c r="G21">
-        <v>-6.154325171446707</v>
+        <v>-8.728976163884379</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.482475432941688</v>
       </c>
       <c r="E22">
-        <v>-17.56320849721227</v>
+        <v>-19.32509735090257</v>
       </c>
       <c r="F22">
-        <v>-3.522787432356729</v>
+        <v>-2.885952655330317</v>
       </c>
       <c r="G22">
-        <v>-6.311830996568611</v>
+        <v>-8.003261544584126</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.048539445177595</v>
       </c>
       <c r="E23">
-        <v>-17.83867557109886</v>
+        <v>-20.07995774018915</v>
       </c>
       <c r="F23">
-        <v>-3.488025822665651</v>
+        <v>-2.871700594165151</v>
       </c>
       <c r="G23">
-        <v>-6.308993859041456</v>
+        <v>-7.633592787486947</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.238062072814844</v>
       </c>
       <c r="E24">
-        <v>-18.17414039711307</v>
+        <v>-20.06310275993261</v>
       </c>
       <c r="F24">
-        <v>-2.810729439849496</v>
+        <v>-2.510510040624691</v>
       </c>
       <c r="G24">
-        <v>-6.898757615226001</v>
+        <v>-8.005251182453227</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.07539265324655</v>
       </c>
       <c r="E25">
-        <v>-18.97280018700184</v>
+        <v>-20.43356363307809</v>
       </c>
       <c r="F25">
-        <v>-2.992000250236709</v>
+        <v>-2.853431779463811</v>
       </c>
       <c r="G25">
-        <v>-6.5457276600092</v>
+        <v>-8.917647464712983</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.595561527776506</v>
       </c>
       <c r="E26">
-        <v>-20.475424846805</v>
+        <v>-20.35438326505398</v>
       </c>
       <c r="F26">
-        <v>-2.746545876745785</v>
+        <v>-2.437300586300077</v>
       </c>
       <c r="G26">
-        <v>-6.030017496992612</v>
+        <v>-8.309341342962982</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.849790237538502</v>
       </c>
       <c r="E27">
-        <v>-19.83796967464128</v>
+        <v>-20.60494373189838</v>
       </c>
       <c r="F27">
-        <v>-2.531896001862766</v>
+        <v>-2.287096866987456</v>
       </c>
       <c r="G27">
-        <v>-7.982709677876329</v>
+        <v>-8.433102777403096</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9017602469416857</v>
       </c>
       <c r="E28">
-        <v>-19.99842256568105</v>
+        <v>-20.70600568632756</v>
       </c>
       <c r="F28">
-        <v>-2.332744052718723</v>
+        <v>-2.701176194094456</v>
       </c>
       <c r="G28">
-        <v>-7.90234949545606</v>
+        <v>-8.397670008496277</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.1785568686642748</v>
       </c>
       <c r="E29">
-        <v>-18.95207788994275</v>
+        <v>-20.27969061477146</v>
       </c>
       <c r="F29">
-        <v>-2.232970512521133</v>
+        <v>-2.434674661633202</v>
       </c>
       <c r="G29">
-        <v>-7.226524797432623</v>
+        <v>-8.378379459638943</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.332294418138996</v>
       </c>
       <c r="E30">
-        <v>-18.52074074071215</v>
+        <v>-20.68900126642876</v>
       </c>
       <c r="F30">
-        <v>-2.89718283221007</v>
+        <v>-2.399060661884643</v>
       </c>
       <c r="G30">
-        <v>-7.489703236168064</v>
+        <v>-9.513704567967682</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.507508377464086</v>
       </c>
       <c r="E31">
-        <v>-18.29103389667307</v>
+        <v>-20.96085008958322</v>
       </c>
       <c r="F31">
-        <v>-2.574341547582212</v>
+        <v>-2.599304399265576</v>
       </c>
       <c r="G31">
-        <v>-7.762435909329843</v>
+        <v>-8.780230029923377</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.654968058464964</v>
       </c>
       <c r="E32">
-        <v>-18.41746436249321</v>
+        <v>-20.22607348252065</v>
       </c>
       <c r="F32">
-        <v>-2.910990888447334</v>
+        <v>-2.675457042972337</v>
       </c>
       <c r="G32">
-        <v>-7.760280744183777</v>
+        <v>-8.915194350468385</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.729047422909011</v>
       </c>
       <c r="E33">
-        <v>-17.75531089309165</v>
+        <v>-20.13890035787299</v>
       </c>
       <c r="F33">
-        <v>-2.976154410188558</v>
+        <v>-2.311691095176573</v>
       </c>
       <c r="G33">
-        <v>-7.720630340259926</v>
+        <v>-9.010455298360913</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.689776226257355</v>
       </c>
       <c r="E34">
-        <v>-17.15703154956828</v>
+        <v>-19.37544492491985</v>
       </c>
       <c r="F34">
-        <v>-2.959467777226564</v>
+        <v>-2.210763639186884</v>
       </c>
       <c r="G34">
-        <v>-7.449010010399343</v>
+        <v>-8.146436018066526</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.500933910729591</v>
       </c>
       <c r="E35">
-        <v>-17.92036018524922</v>
+        <v>-19.11950010248033</v>
       </c>
       <c r="F35">
-        <v>-2.838580808666421</v>
+        <v>-2.524372769110541</v>
       </c>
       <c r="G35">
-        <v>-7.572109335731603</v>
+        <v>-8.711397167070849</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.131238507698004</v>
       </c>
       <c r="E36">
-        <v>-16.7751815642935</v>
+        <v>-18.22350982074469</v>
       </c>
       <c r="F36">
-        <v>-2.564416877729272</v>
+        <v>-2.674715654146831</v>
       </c>
       <c r="G36">
-        <v>-7.112026269411389</v>
+        <v>-8.368351817200491</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.557073530456702</v>
       </c>
       <c r="E37">
-        <v>-16.9322788560936</v>
+        <v>-18.49081658446946</v>
       </c>
       <c r="F37">
-        <v>-3.360593923255988</v>
+        <v>-2.569652159714964</v>
       </c>
       <c r="G37">
-        <v>-7.238293786824732</v>
+        <v>-8.012418513545748</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.763885378891541</v>
       </c>
       <c r="E38">
-        <v>-15.82480430972575</v>
+        <v>-17.93572529755724</v>
       </c>
       <c r="F38">
-        <v>-2.483124214288139</v>
+        <v>-2.191651546469494</v>
       </c>
       <c r="G38">
-        <v>-6.877215895401963</v>
+        <v>-7.831166145270651</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.747840887597985</v>
       </c>
       <c r="E39">
-        <v>-15.51019763499087</v>
+        <v>-17.74448784021332</v>
       </c>
       <c r="F39">
-        <v>-2.628824928399142</v>
+        <v>-2.633844834860107</v>
       </c>
       <c r="G39">
-        <v>-7.255429170535999</v>
+        <v>-7.686194045560427</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.516261217072099</v>
       </c>
       <c r="E40">
-        <v>-16.12209862832931</v>
+        <v>-17.60216243062625</v>
       </c>
       <c r="F40">
-        <v>-2.944631717042425</v>
+        <v>-2.591292429745699</v>
       </c>
       <c r="G40">
-        <v>-6.445845190543849</v>
+        <v>-7.263794919113738</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.086175498038334</v>
       </c>
       <c r="E41">
-        <v>-14.80178580360096</v>
+        <v>-17.1158903632086</v>
       </c>
       <c r="F41">
-        <v>-2.549445793658476</v>
+        <v>-2.723067459448238</v>
       </c>
       <c r="G41">
-        <v>-5.459954797312271</v>
+        <v>-7.167189889732265</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.48343154945124</v>
       </c>
       <c r="E42">
-        <v>-14.17573332898854</v>
+        <v>-16.72063609487111</v>
       </c>
       <c r="F42">
-        <v>-3.036722977946452</v>
+        <v>-2.592020564692759</v>
       </c>
       <c r="G42">
-        <v>-6.05823658716936</v>
+        <v>-7.461348413624207</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.742229573437823</v>
       </c>
       <c r="E43">
-        <v>-13.75599813016559</v>
+        <v>-16.02302014551549</v>
       </c>
       <c r="F43">
-        <v>-2.791640541419385</v>
+        <v>-2.531896001862766</v>
       </c>
       <c r="G43">
-        <v>-5.246431231120358</v>
+        <v>-7.269293735254467</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.904100838562443</v>
       </c>
       <c r="E44">
-        <v>-13.40910343575602</v>
+        <v>-15.52610163570581</v>
       </c>
       <c r="F44">
-        <v>-3.051053734014883</v>
+        <v>-2.715685877521892</v>
       </c>
       <c r="G44">
-        <v>-5.133131120584341</v>
+        <v>-7.151362171509009</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.015381708933815</v>
       </c>
       <c r="E45">
-        <v>-12.98495297477559</v>
+        <v>-15.347331067305</v>
       </c>
       <c r="F45">
-        <v>-3.780958902215431</v>
+        <v>-2.850054525562597</v>
       </c>
       <c r="G45">
-        <v>-6.10756702625004</v>
+        <v>-6.760330464046915</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.127942637063376</v>
       </c>
       <c r="E46">
-        <v>-12.49096438764887</v>
+        <v>-14.98988049998355</v>
       </c>
       <c r="F46">
-        <v>-3.263403232620328</v>
+        <v>-2.771163299222181</v>
       </c>
       <c r="G46">
-        <v>-4.944575688849612</v>
+        <v>-6.940344688290325</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.29580633294762</v>
       </c>
       <c r="E47">
-        <v>-12.7100112038739</v>
+        <v>-14.7613148313944</v>
       </c>
       <c r="F47">
-        <v>-3.382911797822213</v>
+        <v>-3.06740404981134</v>
       </c>
       <c r="G47">
-        <v>-5.825217218296679</v>
+        <v>-6.792144806679311</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.568999561250889</v>
       </c>
       <c r="E48">
-        <v>-11.01095492704002</v>
+        <v>-13.50886118967099</v>
       </c>
       <c r="F48">
-        <v>-3.658129412095724</v>
+        <v>-3.272945196733176</v>
       </c>
       <c r="G48">
-        <v>-5.807062186559316</v>
+        <v>-6.645146653099053</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.9874251702792277</v>
       </c>
       <c r="E49">
-        <v>-10.32725497830997</v>
+        <v>-13.6222768211931</v>
       </c>
       <c r="F49">
-        <v>-3.730826106998005</v>
+        <v>-3.118375981207802</v>
       </c>
       <c r="G49">
-        <v>-5.07299506086348</v>
+        <v>-6.664298159043736</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.5822033783296151</v>
       </c>
       <c r="E50">
-        <v>-11.53810552932491</v>
+        <v>-12.86040635414263</v>
       </c>
       <c r="F50">
-        <v>-3.823338178542654</v>
+        <v>-3.229656372997679</v>
       </c>
       <c r="G50">
-        <v>-5.763310016712308</v>
+        <v>-6.07613339635466</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.3726783554431637</v>
       </c>
       <c r="E51">
-        <v>-10.92764911919492</v>
+        <v>-12.6764778538471</v>
       </c>
       <c r="F51">
-        <v>-4.059292006290871</v>
+        <v>-3.517278789128112</v>
       </c>
       <c r="G51">
-        <v>-5.03183835871926</v>
+        <v>-6.552385167088674</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.3624167245631827</v>
       </c>
       <c r="E52">
-        <v>-10.5481946966702</v>
+        <v>-11.93796978420221</v>
       </c>
       <c r="F52">
-        <v>-4.183171037909926</v>
+        <v>-3.344859912807215</v>
       </c>
       <c r="G52">
-        <v>-4.374940049543836</v>
+        <v>-6.716574983654367</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.5389439004600153</v>
       </c>
       <c r="E53">
-        <v>-10.14950331656089</v>
+        <v>-11.54273362976075</v>
       </c>
       <c r="F53">
-        <v>-3.89405673208705</v>
+        <v>-3.227732075520976</v>
       </c>
       <c r="G53">
-        <v>-4.985891297179716</v>
+        <v>-6.514055670834992</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.8792068084612277</v>
       </c>
       <c r="E54">
-        <v>-10.27083924912241</v>
+        <v>-12.08648108928375</v>
       </c>
       <c r="F54">
-        <v>-4.130159665967772</v>
+        <v>-3.276789649849568</v>
       </c>
       <c r="G54">
-        <v>-4.914287507710819</v>
+        <v>-7.008594895127939</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.351010107956227</v>
       </c>
       <c r="E55">
-        <v>-8.659359131122875</v>
+        <v>-11.02750649953806</v>
       </c>
       <c r="F55">
-        <v>-4.243836524653948</v>
+        <v>-3.486408021127983</v>
       </c>
       <c r="G55">
-        <v>-5.103743407832231</v>
+        <v>-6.807621607075403</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.912402143710816</v>
       </c>
       <c r="E56">
-        <v>-9.385296156922472</v>
+        <v>-11.33820510120432</v>
       </c>
       <c r="F56">
-        <v>-4.233450454157647</v>
+        <v>-3.754846276576982</v>
       </c>
       <c r="G56">
-        <v>-5.367411807307485</v>
+        <v>-6.892030586690201</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.517285153884215</v>
       </c>
       <c r="E57">
-        <v>-7.586676850555959</v>
+        <v>-10.13423783068103</v>
       </c>
       <c r="F57">
-        <v>-4.181183784510609</v>
+        <v>-3.664447370276875</v>
       </c>
       <c r="G57">
-        <v>-5.860901588664484</v>
+        <v>-6.452595392898423</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.12416899462175</v>
       </c>
       <c r="E58">
-        <v>-8.49003948797608</v>
+        <v>-10.74948989478515</v>
       </c>
       <c r="F58">
-        <v>-3.965862932031323</v>
+        <v>-3.880213056051465</v>
       </c>
       <c r="G58">
-        <v>-5.673044682038539</v>
+        <v>-6.542218481737572</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.699800637956618</v>
       </c>
       <c r="E59">
-        <v>-6.568712121423724</v>
+        <v>-9.387637377984436</v>
       </c>
       <c r="F59">
-        <v>-3.98197964822019</v>
+        <v>-3.608820842444083</v>
       </c>
       <c r="G59">
-        <v>-5.224379687283273</v>
+        <v>-6.03284470288315</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.216426776576838</v>
       </c>
       <c r="E60">
-        <v>-7.055735915526648</v>
+        <v>-9.525783006062429</v>
       </c>
       <c r="F60">
-        <v>-4.637326779964366</v>
+        <v>-3.817563629377739</v>
       </c>
       <c r="G60">
-        <v>-5.629520939833741</v>
+        <v>-6.579164169955838</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.652346858599699</v>
       </c>
       <c r="E61">
-        <v>-6.587278864855173</v>
+        <v>-9.643586728897965</v>
       </c>
       <c r="F61">
-        <v>-4.430399774377646</v>
+        <v>-3.941924770825223</v>
       </c>
       <c r="G61">
-        <v>-5.882920027046175</v>
+        <v>-7.057233430190912</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.992850764897052</v>
       </c>
       <c r="E62">
-        <v>-6.080714705409151</v>
+        <v>-8.974400539362493</v>
       </c>
       <c r="F62">
-        <v>-4.501035491181763</v>
+        <v>-3.99817423094492</v>
       </c>
       <c r="G62">
-        <v>-5.304868980979573</v>
+        <v>-6.746220918958541</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.230869307170516</v>
       </c>
       <c r="E63">
-        <v>-7.428148560969443</v>
+        <v>-9.410610326625349</v>
       </c>
       <c r="F63">
-        <v>-4.5395131570418</v>
+        <v>-3.818676955167101</v>
       </c>
       <c r="G63">
-        <v>-6.514532389392647</v>
+        <v>-7.185937509121158</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.364503468152308</v>
       </c>
       <c r="E64">
-        <v>-6.691225457227238</v>
+        <v>-8.180269223481389</v>
       </c>
       <c r="F64">
-        <v>-4.622410368142155</v>
+        <v>-4.090293656340642</v>
       </c>
       <c r="G64">
-        <v>-6.440869440598324</v>
+        <v>-6.588685298926783</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.397153265905562</v>
       </c>
       <c r="E65">
-        <v>-6.086384354866754</v>
+        <v>-8.630766346238444</v>
       </c>
       <c r="F65">
-        <v>-4.446656484657587</v>
+        <v>-3.975083489591884</v>
       </c>
       <c r="G65">
-        <v>-6.101922546105583</v>
+        <v>-7.268413130141021</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.337274813800567</v>
       </c>
       <c r="E66">
-        <v>-6.489672136093845</v>
+        <v>-8.906464372299423</v>
       </c>
       <c r="F66">
-        <v>-4.657500011324742</v>
+        <v>-3.931319182967181</v>
       </c>
       <c r="G66">
-        <v>-6.40827049867312</v>
+        <v>-7.246030531750009</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.199115622986465</v>
       </c>
       <c r="E67">
-        <v>-4.617288516616391</v>
+        <v>-8.833098564901157</v>
       </c>
       <c r="F67">
-        <v>-4.629589828422218</v>
+        <v>-3.953743916928366</v>
       </c>
       <c r="G67">
-        <v>-6.571924006861452</v>
+        <v>-7.30589181619111</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.999837056278878</v>
       </c>
       <c r="E68">
-        <v>-6.241013628332666</v>
+        <v>-8.770954316093896</v>
       </c>
       <c r="F68">
-        <v>-4.663458458053079</v>
+        <v>-3.86136272743336</v>
       </c>
       <c r="G68">
-        <v>-5.461586896263132</v>
+        <v>-7.097870376685465</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.758830459326017</v>
       </c>
       <c r="E69">
-        <v>-5.211084670872166</v>
+        <v>-7.451243778408561</v>
       </c>
       <c r="F69">
-        <v>-4.941610978034708</v>
+        <v>-4.208902614543087</v>
       </c>
       <c r="G69">
-        <v>-5.685661171088702</v>
+        <v>-7.003023246985347</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.496233644642982</v>
       </c>
       <c r="E70">
-        <v>-6.419711741149346</v>
+        <v>-8.128852929598301</v>
       </c>
       <c r="F70">
-        <v>-4.73861374740687</v>
+        <v>-4.105873590452496</v>
       </c>
       <c r="G70">
-        <v>-5.510417442967382</v>
+        <v>-7.202996750285022</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.232764101456312</v>
       </c>
       <c r="E71">
-        <v>-6.133688794350879</v>
+        <v>-8.447566930258139</v>
       </c>
       <c r="F71">
-        <v>-5.173898451658134</v>
+        <v>-4.594630238921871</v>
       </c>
       <c r="G71">
-        <v>-5.911327818318662</v>
+        <v>-6.618298128775563</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.984257970908907</v>
       </c>
       <c r="E72">
-        <v>-5.565039256259697</v>
+        <v>-7.874950448936239</v>
       </c>
       <c r="F72">
-        <v>-5.128288542459994</v>
+        <v>-4.264503462986392</v>
       </c>
       <c r="G72">
-        <v>-5.713645212532161</v>
+        <v>-6.735845669238465</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.760750336514283</v>
       </c>
       <c r="E73">
-        <v>-5.722530525298456</v>
+        <v>-8.769926352494155</v>
       </c>
       <c r="F73">
-        <v>-5.202425768275743</v>
+        <v>-4.279559868899676</v>
       </c>
       <c r="G73">
-        <v>-5.255032028431384</v>
+        <v>-6.86396378160826</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.566579448712539</v>
       </c>
       <c r="E74">
-        <v>-6.515892000598257</v>
+        <v>-8.621464860626689</v>
       </c>
       <c r="F74">
-        <v>-5.028288029594037</v>
+        <v>-4.225923907935811</v>
       </c>
       <c r="G74">
-        <v>-5.355702407735082</v>
+        <v>-6.486945613413901</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.403986457350896</v>
       </c>
       <c r="E75">
-        <v>-5.813503039638546</v>
+        <v>-8.654169499910084</v>
       </c>
       <c r="F75">
-        <v>-5.560742715295892</v>
+        <v>-4.681381843547451</v>
       </c>
       <c r="G75">
-        <v>-4.716022245909407</v>
+        <v>-6.355305080590321</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.269823643845832</v>
       </c>
       <c r="E76">
-        <v>-6.493562095266435</v>
+        <v>-9.081154785619315</v>
       </c>
       <c r="F76">
-        <v>-5.867372849850963</v>
+        <v>-4.577917098202988</v>
       </c>
       <c r="G76">
-        <v>-4.977906261338994</v>
+        <v>-5.920180217090673</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.157357240633773</v>
       </c>
       <c r="E77">
-        <v>-8.098475925954848</v>
+        <v>-9.48389009301747</v>
       </c>
       <c r="F77">
-        <v>-4.973799678572691</v>
+        <v>-4.553585462480558</v>
       </c>
       <c r="G77">
-        <v>-5.302551599102083</v>
+        <v>-6.283797296942063</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.058527037659536</v>
       </c>
       <c r="E78">
-        <v>-7.321738478737204</v>
+        <v>-9.378109468672299</v>
       </c>
       <c r="F78">
-        <v>-5.509212464269943</v>
+        <v>-4.907335620009073</v>
       </c>
       <c r="G78">
-        <v>-5.19241637010161</v>
+        <v>-6.138629875045021</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.967860644000147</v>
       </c>
       <c r="E79">
-        <v>-8.251968552444835</v>
+        <v>-10.4135314651041</v>
       </c>
       <c r="F79">
-        <v>-5.697098616735913</v>
+        <v>-5.188332753651916</v>
       </c>
       <c r="G79">
-        <v>-5.095870930539844</v>
+        <v>-6.033132720345066</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.879167102003497</v>
       </c>
       <c r="E80">
-        <v>-9.538412920069822</v>
+        <v>-10.62092651770739</v>
       </c>
       <c r="F80">
-        <v>-5.53576826646889</v>
+        <v>-5.180300903314372</v>
       </c>
       <c r="G80">
-        <v>-3.857856010128451</v>
+        <v>-5.526927133571728</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.787380953209338</v>
       </c>
       <c r="E81">
-        <v>-9.528432163356916</v>
+        <v>-11.62755194792442</v>
       </c>
       <c r="F81">
-        <v>-5.670487313920979</v>
+        <v>-5.128783077799465</v>
       </c>
       <c r="G81">
-        <v>-4.012091016257557</v>
+        <v>-5.373052976906402</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.688100172142915</v>
       </c>
       <c r="E82">
-        <v>-10.88628603760886</v>
+        <v>-12.67308602681535</v>
       </c>
       <c r="F82">
-        <v>-5.795022412523052</v>
+        <v>-4.898225235313084</v>
       </c>
       <c r="G82">
-        <v>-3.691196526590461</v>
+        <v>-5.41144537352533</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.579577403864584</v>
       </c>
       <c r="E83">
-        <v>-12.60172633340248</v>
+        <v>-13.06225855456053</v>
       </c>
       <c r="F83">
-        <v>-5.970761385394369</v>
+        <v>-5.307082534312836</v>
       </c>
       <c r="G83">
-        <v>-4.067291052579365</v>
+        <v>-5.381703432400518</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.459038189287992</v>
       </c>
       <c r="E84">
-        <v>-11.6794346746303</v>
+        <v>-13.85148100461732</v>
       </c>
       <c r="F84">
-        <v>-6.267842100529967</v>
+        <v>-5.450810077270369</v>
       </c>
       <c r="G84">
-        <v>-4.001305258890612</v>
+        <v>-4.915409782648632</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.323223895637747</v>
       </c>
       <c r="E85">
-        <v>-13.50684149026357</v>
+        <v>-14.13168033384193</v>
       </c>
       <c r="F85">
-        <v>-6.306959266024966</v>
+        <v>-5.812167961026195</v>
       </c>
       <c r="G85">
-        <v>-4.400335244375586</v>
+        <v>-5.116220853969744</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.168533310737976</v>
       </c>
       <c r="E86">
-        <v>-14.63139744058835</v>
+        <v>-15.69384536989793</v>
       </c>
       <c r="F86">
-        <v>-6.757427530585844</v>
+        <v>-5.720661527508545</v>
       </c>
       <c r="G86">
-        <v>-4.919531411845025</v>
+        <v>-4.239624811171665</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.994780206909966</v>
       </c>
       <c r="E87">
-        <v>-16.0388471621723</v>
+        <v>-17.24692175862054</v>
       </c>
       <c r="F87">
-        <v>-6.349980941273059</v>
+        <v>-5.671207165194012</v>
       </c>
       <c r="G87">
-        <v>-4.705190140904912</v>
+        <v>-5.075623634021661</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.80422251079457</v>
       </c>
       <c r="E88">
-        <v>-16.62435620899404</v>
+        <v>-17.47440965039586</v>
       </c>
       <c r="F88">
-        <v>-6.526887912182324</v>
+        <v>-5.779655368833717</v>
       </c>
       <c r="G88">
-        <v>-4.007873381240525</v>
+        <v>-4.305084228119675</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.602912480428815</v>
       </c>
       <c r="E89">
-        <v>-17.92026508729505</v>
+        <v>-19.5595002224876</v>
       </c>
       <c r="F89">
-        <v>-6.794115094488431</v>
+        <v>-6.127368384730629</v>
       </c>
       <c r="G89">
-        <v>-3.892434658286139</v>
+        <v>-4.801391283730593</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.399383788500724</v>
       </c>
       <c r="E90">
-        <v>-20.51438330869299</v>
+        <v>-21.44795539621828</v>
       </c>
       <c r="F90">
-        <v>-6.417851153502929</v>
+        <v>-6.139280307982887</v>
       </c>
       <c r="G90">
-        <v>-4.263761998698492</v>
+        <v>-4.770947506951456</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.20712146960409</v>
       </c>
       <c r="E91">
-        <v>-22.34648615187222</v>
+        <v>-22.82083927570168</v>
       </c>
       <c r="F91">
-        <v>-7.19702098788277</v>
+        <v>-6.123316011396135</v>
       </c>
       <c r="G91">
-        <v>-3.076222966124367</v>
+        <v>-5.239710823675638</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.040627329749092</v>
       </c>
       <c r="E92">
-        <v>-24.48284357820479</v>
+        <v>-25.08184747756939</v>
       </c>
       <c r="F92">
-        <v>-7.123471488739305</v>
+        <v>-6.20970479109929</v>
       </c>
       <c r="G92">
-        <v>-4.751885385736331</v>
+        <v>-5.437479503646159</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.9166794010420927</v>
       </c>
       <c r="E93">
-        <v>-26.24849106532146</v>
+        <v>-26.89628021517068</v>
       </c>
       <c r="F93">
-        <v>-6.898937119822381</v>
+        <v>-6.489348786589659</v>
       </c>
       <c r="G93">
-        <v>-5.075060841279985</v>
+        <v>-5.297085888416746</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.8524931630661512</v>
       </c>
       <c r="E94">
-        <v>-29.17603177095614</v>
+        <v>-28.87215757961944</v>
       </c>
       <c r="F94">
-        <v>-7.609314354869334</v>
+        <v>-6.273347430288973</v>
       </c>
       <c r="G94">
-        <v>-4.690348965252359</v>
+        <v>-5.665387390206205</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.8647781910731364</v>
       </c>
       <c r="E95">
-        <v>-30.00628219552243</v>
+        <v>-31.19177329209442</v>
       </c>
       <c r="F95">
-        <v>-6.827798998188467</v>
+        <v>-6.119792964832028</v>
       </c>
       <c r="G95">
-        <v>-5.555490520484559</v>
+        <v>-6.051039461166985</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.9686411888774353</v>
       </c>
       <c r="E96">
-        <v>-33.07322518077223</v>
+        <v>-32.94746719334222</v>
       </c>
       <c r="F96">
-        <v>-6.888736603624309</v>
+        <v>-6.396070475197421</v>
       </c>
       <c r="G96">
-        <v>-5.893076780760659</v>
+        <v>-6.567557397295154</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.160464792889781</v>
       </c>
       <c r="E97">
-        <v>-35.34036267220932</v>
+        <v>-36.19389624588604</v>
       </c>
       <c r="F97">
-        <v>-7.148137370708765</v>
+        <v>-6.59895546204218</v>
       </c>
       <c r="G97">
-        <v>-6.386162675561867</v>
+        <v>-6.824826512242996</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.442767194267703</v>
       </c>
       <c r="E98">
-        <v>-37.06909856768947</v>
+        <v>-38.51930840509084</v>
       </c>
       <c r="F98">
-        <v>-6.91507206009411</v>
+        <v>-6.549372702780213</v>
       </c>
       <c r="G98">
-        <v>-6.767242883132913</v>
+        <v>-7.655045122581424</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.785248370962294</v>
       </c>
       <c r="E99">
-        <v>-41.07452024205188</v>
+        <v>-40.10961564286752</v>
       </c>
       <c r="F99">
-        <v>-7.806941279624823</v>
+        <v>-6.605154135317329</v>
       </c>
       <c r="G99">
-        <v>-7.393230628608163</v>
+        <v>-8.073021360187647</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.194582882262763</v>
       </c>
       <c r="E100">
-        <v>-42.87299237301314</v>
+        <v>-42.65319156586584</v>
       </c>
       <c r="F100">
-        <v>-7.065091467659608</v>
+        <v>-6.513058318392586</v>
       </c>
       <c r="G100">
-        <v>-7.673458376870851</v>
+        <v>-8.263533324336086</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.605741825741009</v>
       </c>
       <c r="E101">
-        <v>-44.99982415427058</v>
+        <v>-45.09123819482642</v>
       </c>
       <c r="F101">
-        <v>-7.454496214939419</v>
+        <v>-6.496050693062008</v>
       </c>
       <c r="G101">
-        <v>-7.171649194573663</v>
+        <v>-8.201602948932941</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.06814354328274</v>
       </c>
       <c r="E102">
-        <v>-47.04285652401608</v>
+        <v>-47.49190453509068</v>
       </c>
       <c r="F102">
-        <v>-7.184479091220684</v>
+        <v>-6.377166716881835</v>
       </c>
       <c r="G102">
-        <v>-8.60219551191245</v>
+        <v>-9.548438811765715</v>
       </c>
     </row>
   </sheetData>
